--- a/data/trans_orig/IQ27A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ27A-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Talla media, en centímetros, referida por progenitor/a</t>
+          <t>Talla media, en centímetros, declarada por progenitor/a (tasa de respuesta: 90,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>121,15; 129,55</t>
+          <t>121,23; 129,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>119,09; 128,39</t>
+          <t>119,35; 128,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>119,02; 128,52</t>
+          <t>118,81; 128,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>126,39; 134,83</t>
+          <t>126,49; 134,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>124,92; 134,3</t>
+          <t>125,03; 134,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>119,55; 129,98</t>
+          <t>119,27; 129,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>119,65; 128,92</t>
+          <t>119,52; 129,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>131,9; 145,58</t>
+          <t>132,58; 145,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>124,65; 131,02</t>
+          <t>124,77; 131,02</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>120,77; 127,81</t>
+          <t>120,76; 127,81</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>120,7; 127,48</t>
+          <t>120,63; 127,52</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>130,77; 139,56</t>
+          <t>131,23; 140,23</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>123,4; 130,76</t>
+          <t>123,84; 131,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>117,53; 124,93</t>
+          <t>117,77; 125,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>120,33; 127,43</t>
+          <t>120,13; 127,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>127,04; 135,58</t>
+          <t>126,86; 135,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>123,81; 130,81</t>
+          <t>124,16; 130,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>118,03; 125,55</t>
+          <t>118,43; 125,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>120,57; 127,9</t>
+          <t>120,44; 127,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>131,71; 138,74</t>
+          <t>132,01; 138,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>125,07; 130,09</t>
+          <t>124,86; 129,86</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>119,18; 124,27</t>
+          <t>119,11; 124,12</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>121,37; 126,24</t>
+          <t>121,36; 126,32</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>130,87; 136,5</t>
+          <t>131,21; 136,51</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>120,86; 129,92</t>
+          <t>121,16; 129,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>115,39; 123,98</t>
+          <t>115,66; 124,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>119,56; 127,51</t>
+          <t>119,54; 127,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>133,26; 146,66</t>
+          <t>133,42; 146,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>121,0; 130,81</t>
+          <t>121,34; 130,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>116,28; 125,23</t>
+          <t>116,65; 125,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>122,09; 130,06</t>
+          <t>121,74; 129,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>134,86; 143,86</t>
+          <t>135,17; 143,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>122,73; 128,86</t>
+          <t>122,3; 128,91</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>117,21; 123,57</t>
+          <t>117,36; 123,84</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>122,08; 127,73</t>
+          <t>122,17; 127,65</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>135,77; 144,4</t>
+          <t>135,48; 144,08</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>122,13; 129,02</t>
+          <t>121,82; 129,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>116,34; 124,74</t>
+          <t>116,77; 125,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>117,55; 125,31</t>
+          <t>117,07; 125,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>126,54; 134,83</t>
+          <t>126,68; 134,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>123,33; 130,79</t>
+          <t>123,18; 131,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>120,05; 127,95</t>
+          <t>120,15; 128,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>120,09; 127,73</t>
+          <t>120,12; 127,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>131,66; 139,46</t>
+          <t>131,51; 139,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>123,68; 128,86</t>
+          <t>123,96; 129,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>119,54; 125,13</t>
+          <t>119,58; 125,14</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>119,99; 125,42</t>
+          <t>120,04; 125,23</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>130,65; 136,09</t>
+          <t>130,31; 136,14</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>124,21; 128,03</t>
+          <t>124,21; 128,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>119,23; 123,39</t>
+          <t>119,47; 123,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>121,04; 125,13</t>
+          <t>121,09; 125,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>131,21; 137,15</t>
+          <t>131,05; 137,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>125,69; 129,42</t>
+          <t>125,39; 129,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>120,6; 124,97</t>
+          <t>120,89; 125,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>122,47; 126,53</t>
+          <t>122,44; 126,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>134,73; 139,46</t>
+          <t>134,57; 139,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>125,5; 128,29</t>
+          <t>125,42; 128,28</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>120,65; 123,68</t>
+          <t>120,6; 123,63</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>122,35; 125,16</t>
+          <t>122,48; 125,23</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>133,61; 137,29</t>
+          <t>133,66; 137,31</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ27A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ27A-Habitat-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>121,23; 129,88</t>
+          <t>120,72; 129,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>119,35; 128,82</t>
+          <t>119,13; 128,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>118,81; 128,65</t>
+          <t>118,68; 128,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>126,49; 134,8</t>
+          <t>126,31; 134,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>125,03; 134,24</t>
+          <t>124,6; 134,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>119,27; 129,64</t>
+          <t>119,63; 129,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>119,52; 129,48</t>
+          <t>119,41; 129,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>132,58; 145,97</t>
+          <t>132,5; 146,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>124,77; 131,02</t>
+          <t>124,6; 131,34</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>120,76; 127,81</t>
+          <t>120,71; 127,66</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>120,63; 127,52</t>
+          <t>120,71; 127,42</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>131,23; 140,23</t>
+          <t>131,04; 140,1</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>123,84; 131,1</t>
+          <t>123,79; 130,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>117,77; 125,08</t>
+          <t>117,61; 124,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>120,13; 127,41</t>
+          <t>120,59; 127,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>126,86; 135,4</t>
+          <t>127,13; 135,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>124,16; 130,91</t>
+          <t>124,03; 130,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>118,43; 125,63</t>
+          <t>118,09; 125,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>120,44; 127,39</t>
+          <t>120,14; 127,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>132,01; 138,97</t>
+          <t>131,94; 138,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>124,86; 129,86</t>
+          <t>124,96; 129,89</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>119,11; 124,12</t>
+          <t>118,97; 124,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>121,36; 126,32</t>
+          <t>121,36; 126,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>131,21; 136,51</t>
+          <t>130,91; 136,52</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>121,16; 129,8</t>
+          <t>120,91; 129,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>115,66; 124,25</t>
+          <t>115,5; 123,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>119,54; 127,92</t>
+          <t>119,94; 127,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>133,42; 146,85</t>
+          <t>133,29; 147,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>121,34; 130,84</t>
+          <t>121,64; 130,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>116,65; 125,2</t>
+          <t>116,79; 125,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>121,74; 129,38</t>
+          <t>121,61; 129,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>135,17; 143,88</t>
+          <t>135,45; 144,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>122,3; 128,91</t>
+          <t>122,43; 128,95</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>117,36; 123,84</t>
+          <t>117,24; 123,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>122,17; 127,65</t>
+          <t>122,05; 127,47</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>135,48; 144,08</t>
+          <t>135,46; 143,75</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>121,82; 129,47</t>
+          <t>121,87; 129,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>116,77; 125,29</t>
+          <t>117,15; 125,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>117,07; 125,51</t>
+          <t>117,55; 124,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>126,68; 134,88</t>
+          <t>126,62; 134,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>123,18; 131,0</t>
+          <t>123,11; 130,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>120,15; 128,11</t>
+          <t>120,41; 127,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>120,12; 127,95</t>
+          <t>120,19; 128,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>131,51; 139,33</t>
+          <t>131,96; 139,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>123,96; 129,21</t>
+          <t>123,55; 128,98</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>119,58; 125,14</t>
+          <t>119,73; 125,31</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>120,04; 125,23</t>
+          <t>119,8; 125,29</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>130,31; 136,14</t>
+          <t>130,64; 136,22</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>124,21; 128,07</t>
+          <t>124,07; 128,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>119,47; 123,72</t>
+          <t>119,31; 123,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>121,09; 125,16</t>
+          <t>121,11; 124,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>131,05; 137,31</t>
+          <t>131,1; 137,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>125,39; 129,53</t>
+          <t>125,48; 129,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>120,89; 125,19</t>
+          <t>120,66; 124,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>122,44; 126,57</t>
+          <t>122,5; 126,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>134,57; 139,15</t>
+          <t>134,74; 139,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>125,42; 128,28</t>
+          <t>125,32; 128,2</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>120,6; 123,63</t>
+          <t>120,75; 123,51</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>122,48; 125,23</t>
+          <t>122,25; 125,1</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>133,66; 137,31</t>
+          <t>133,62; 137,31</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ27A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ27A-Habitat-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>129,75</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>124,57</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>124,34</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>137,5</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>125,46</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>124,05</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>123,82</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>130,7</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>129,75</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>124,57</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>124,34</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>138,03</t>
+          <t>132,42</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>134,78</t>
+          <t>135,08</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>120,72; 129,86</t>
+          <t>124,92; 134,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>119,13; 128,47</t>
+          <t>119,55; 129,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>118,68; 128,85</t>
+          <t>119,65; 128,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>126,31; 134,72</t>
+          <t>132,29; 142,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>124,6; 134,27</t>
+          <t>121,15; 129,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>119,63; 129,82</t>
+          <t>119,09; 128,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>119,41; 129,17</t>
+          <t>119,02; 128,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>132,5; 146,25</t>
+          <t>128,05; 136,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>124,6; 131,34</t>
+          <t>124,65; 131,02</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>120,71; 127,66</t>
+          <t>120,77; 127,81</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>120,71; 127,42</t>
+          <t>120,7; 127,48</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>131,04; 140,1</t>
+          <t>131,81; 138,41</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>127,43</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121,76</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>124,01</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>137,27</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>127,42</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>121,44</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>124,03</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>132,1</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>127,43</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>121,76</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>124,01</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>135,35</t>
+          <t>135,05</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>133,94</t>
+          <t>136,28</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>123,79; 130,95</t>
+          <t>123,81; 130,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>117,61; 124,73</t>
+          <t>118,03; 125,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>120,59; 127,7</t>
+          <t>120,57; 127,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>127,13; 135,46</t>
+          <t>133,68; 140,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>124,03; 130,93</t>
+          <t>123,4; 130,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>118,09; 125,12</t>
+          <t>117,53; 124,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>120,14; 127,12</t>
+          <t>120,33; 127,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>131,94; 138,87</t>
+          <t>131,97; 138,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>124,96; 129,89</t>
+          <t>125,07; 130,09</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>118,97; 124,36</t>
+          <t>119,18; 124,27</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>121,36; 126,62</t>
+          <t>121,37; 126,24</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>130,91; 136,52</t>
+          <t>133,88; 138,65</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>126,28</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>121,0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>125,72</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>140,66</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>125,32</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>119,77</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>123,73</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>138,68</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>126,28</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>121,0</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>125,72</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>139,27</t>
+          <t>135,16</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>138,98</t>
+          <t>138,07</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>120,91; 129,36</t>
+          <t>121,0; 130,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>115,5; 123,85</t>
+          <t>116,28; 125,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>119,94; 127,54</t>
+          <t>122,09; 130,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>133,29; 147,16</t>
+          <t>136,3; 145,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>121,64; 130,83</t>
+          <t>120,86; 129,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>116,79; 125,91</t>
+          <t>115,39; 123,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>121,61; 129,34</t>
+          <t>119,56; 127,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>135,45; 144,04</t>
+          <t>131,19; 138,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>122,43; 128,95</t>
+          <t>122,73; 128,86</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>117,24; 123,75</t>
+          <t>117,21; 123,57</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>122,05; 127,47</t>
+          <t>122,08; 127,73</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>135,46; 143,75</t>
+          <t>135,28; 141,23</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>127,06</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>124,11</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>124,07</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>136,2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>125,7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>121,08</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>121,28</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>131,12</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>127,06</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>124,11</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>124,07</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>135,58</t>
+          <t>133,06</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>133,42</t>
+          <t>134,63</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>121,87; 129,12</t>
+          <t>123,33; 130,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>117,15; 125,12</t>
+          <t>120,05; 127,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>117,55; 124,99</t>
+          <t>120,09; 127,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>126,62; 134,95</t>
+          <t>132,13; 140,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>123,11; 130,86</t>
+          <t>122,13; 129,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>120,41; 127,95</t>
+          <t>116,34; 124,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>120,19; 128,14</t>
+          <t>117,55; 125,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>131,96; 139,63</t>
+          <t>129,21; 136,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>123,55; 128,98</t>
+          <t>123,68; 128,86</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>119,73; 125,31</t>
+          <t>119,54; 125,13</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>119,8; 125,29</t>
+          <t>119,99; 125,42</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>130,64; 136,22</t>
+          <t>132,13; 137,24</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>127,6</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>122,81</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>124,47</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>137,89</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>126,08</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>121,45</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>123,11</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>133,48</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>127,6</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>122,81</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>124,47</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>136,87</t>
+          <t>134,06</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>135,29</t>
+          <t>136,09</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>124,07; 128,06</t>
+          <t>125,69; 129,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>119,31; 123,53</t>
+          <t>120,6; 124,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>121,11; 124,97</t>
+          <t>122,47; 126,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>131,1; 137,36</t>
+          <t>135,81; 140,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>125,48; 129,75</t>
+          <t>124,21; 128,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>120,66; 124,97</t>
+          <t>119,23; 123,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>122,5; 126,43</t>
+          <t>121,04; 125,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>134,74; 139,18</t>
+          <t>132,4; 135,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>125,32; 128,2</t>
+          <t>125,5; 128,29</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>120,75; 123,51</t>
+          <t>120,65; 123,68</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>122,25; 125,1</t>
+          <t>122,35; 125,16</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>133,62; 137,31</t>
+          <t>134,74; 137,44</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ27A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ27A-Habitat-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Talla media, en centímetros, declarada por progenitor/a (tasa de respuesta: 90,55%)</t>
+          <t>Talla media, en centímetros, declarada por madres/padres (tasa de respuesta: 90,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>129,75</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>124,57</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>124,34</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>137,5</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>125,46</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>124,05</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>123,82</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>132,42</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>127,73</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>124,33</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>124,09</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>135,08</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>129.7518108833796</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>124.5720305348875</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>124.3389305379755</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>137.5005113357232</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>125.4618379819344</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>124.052358333812</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>123.8176759270623</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>132.4178871571429</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>127.7292101623399</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>124.3274157098033</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>124.0881802155269</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>135.0758306153411</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>124,92; 134,3</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>119,55; 129,98</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>119,65; 128,92</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>132,29; 142,51</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>121,15; 129,55</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>119,09; 128,39</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>119,02; 128,52</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>128,05; 136,33</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>124,65; 131,02</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>120,77; 127,81</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>120,7; 127,48</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>131,81; 138,41</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>124.9241326233765</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>119.5524797615377</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>119.6511978653474</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>132.2923015327125</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>121.1471449664225</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>119.0873692233664</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>119.0229351922184</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>128.0468335837652</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>124.645406697823</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>120.7707141036772</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>120.7043644700863</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>131.8071762216861</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>134.3039806873754</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>129.9797827468461</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>128.9229051012666</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>142.5102922929677</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>129.5546935857765</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>128.3872985791583</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>128.5188179978098</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>136.3321860950831</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>131.0244071835782</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>127.8118301737302</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>127.4834208341032</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>138.4093636558097</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>127,43</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>121,76</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>124,01</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>137,27</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>127,42</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>121,44</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>124,03</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>135,05</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>127,42</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>121,61</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>124,02</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>136,28</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>123,81; 130,81</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>118,03; 125,55</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>120,57; 127,9</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>133,68; 140,51</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>123,4; 130,76</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>117,53; 124,93</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>120,33; 127,43</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>131,97; 138,52</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>125,07; 130,09</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>119,18; 124,27</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>121,37; 126,24</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>133,88; 138,65</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>127.4255068613275</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>121.7634833569146</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>124.0101953232816</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>137.2697635279378</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>127.4231613947849</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>121.4449060010276</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>124.0312682157304</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>135.0471230601506</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>127.4243698457273</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>121.6093403667432</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>124.0202133819519</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>136.2844535117858</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>126,28</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>121,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>125,72</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>140,66</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>125,32</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>119,77</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>123,73</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>135,16</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>125,82</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>120,41</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>124,75</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>138,07</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>123.8053733221876</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>118.0266056986882</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>120.5701683323004</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>133.6807283328756</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>123.4032113970047</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>117.5272834512225</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>120.3323766097899</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>131.9673480434474</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>125.0680866417223</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>119.1844397897607</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>121.3695087709347</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>133.8834543429563</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>121,0; 130,81</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>116,28; 125,23</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>122,09; 130,06</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>136,3; 145,31</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>120,86; 129,92</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>115,39; 123,98</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>119,56; 127,51</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>131,19; 138,6</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>122,73; 128,86</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>117,21; 123,57</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>122,08; 127,73</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>135,28; 141,23</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>130.8076637294096</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>125.5539871531401</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>127.9016078183298</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>140.5122823557011</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>130.7591029071877</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>124.926419648974</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>127.4317755188455</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>138.5159736904012</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>130.0852151735456</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>124.2686497456704</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>126.2371354861172</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>138.6493683534358</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,277 +923,405 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>127,06</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>124,11</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>124,07</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>136,2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>125,7</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>121,08</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>121,28</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>133,06</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>126,38</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>122,58</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>122,68</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>134,63</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>126.2819654778128</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>121.0034891252663</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>125.7215161645136</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>140.6641070465691</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>125.3212136328704</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>119.7714992194517</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>123.7310480268279</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>135.1596490946656</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>125.8206561037201</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>120.405952459179</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>124.7515384067673</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>138.0732477858992</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>123,33; 130,79</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>120,05; 127,95</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>120,09; 127,73</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>132,13; 140,04</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>122,13; 129,02</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>116,34; 124,74</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>117,55; 125,31</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>129,21; 136,6</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>123,68; 128,86</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>119,54; 125,13</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>119,99; 125,42</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>132,13; 137,24</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>120.9974369521429</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>116.2832022221688</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>122.0942223790459</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>136.2960427112648</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>120.8602205086463</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>115.3862736619017</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>119.5558006995178</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>131.188685281805</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>122.7324677378733</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>117.2056754969079</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>122.0775987727998</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>135.2842442744117</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>130.8059266619885</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>125.2335255968574</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>130.0597737545565</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>145.3054770405836</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>129.9217343583643</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>123.9757605116729</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>127.5081761424501</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>138.5959302337432</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>128.8626781332866</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>123.5692809760968</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>127.7310298793549</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>141.2327035251587</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>127.0588463300759</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>124.1073278014861</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>124.074324235541</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>136.2001100322495</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>125.6984799061543</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>121.0779585165033</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>121.2837812675112</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>133.0580764658686</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>126.378173633582</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>122.5830335840364</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>122.6791324273758</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>134.6292336799559</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>123.3269253233325</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>120.0541672043138</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>120.089921594377</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>132.1269323488174</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>122.1268682906678</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>116.3384592698244</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>117.551725971496</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>129.2069480585937</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>123.6788097353979</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>119.539525668231</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>119.9857289077586</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>132.1316644879171</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>130.787562792451</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>127.9478727855212</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>127.7346104405368</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>140.0385813956885</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>129.024417112358</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>124.744013822186</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>125.3065831739999</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>136.6025931152535</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>128.8563184696205</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>125.1349667721397</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>125.421835389182</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>137.2435946318751</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>127,6</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>122,81</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>124,47</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>137,89</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>126,08</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>121,45</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>123,11</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>134,06</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>126,86</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>122,15</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>123,81</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>136,09</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>125,69; 129,42</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>120,6; 124,97</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>122,47; 126,53</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>135,81; 140,04</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>124,21; 128,03</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>119,23; 123,39</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>121,04; 125,13</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>132,4; 135,87</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>125,5; 128,29</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>120,65; 123,68</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>122,35; 125,16</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>134,74; 137,44</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>127.6017142499947</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>122.8082641514343</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>124.4699673129261</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>137.8890378198919</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>126.0817349585735</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>121.451920198091</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>123.1076750004209</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>134.0592977758161</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>126.8636054164643</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>122.147561154295</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>123.8076008298541</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>136.0873286923118</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>125.692400831572</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>120.5973789900827</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>122.4716574692994</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>135.8101720034165</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>124.2082189124435</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>119.2276281825091</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>121.0442523413011</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>132.4042399224872</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>125.504495408449</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>120.6481000779833</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>122.3508589096817</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>134.7375526166087</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>129.4201798362878</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>124.9701962895935</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>126.5275194843106</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>140.0382938452524</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>128.0270864039212</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>123.3851391296335</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>125.1316997948789</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>135.8716835821866</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>128.2946685045747</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>123.6840150480085</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>125.1572965178322</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>137.4425700959613</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1344,15 +1329,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
